--- a/case_studies/Free_MPW_anti_cracker/2040/technologies.xlsx
+++ b/case_studies/Free_MPW_anti_cracker/2040/technologies.xlsx
@@ -691,37 +691,37 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>114.1</v>
+        <v>70.69</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>195.38</v>
+        <v>172.08</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>21.09</v>
+        <v>141.38</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>983.99</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>228.2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>273.75</v>
+        <v>1526.74</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>36.8</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>22.37</v>
+        <v>1038.6</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>49.16</v>
+        <v>39.33</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>23.43</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -779,13 +779,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>17.75</v>
@@ -794,7 +794,7 @@
         <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>35.22</v>
+        <v>32.33</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>48.42</v>
+        <v>44.45</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.56</v>
+        <v>8.52</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>7.07</v>
@@ -885,49 +885,49 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>102.51</v>
+        <v>26.13</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>250.14</v>
+        <v>153.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>20.3</v>
+        <v>29.96</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1369.36</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1502.3</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>229.43</v>
+        <v>31.96</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>265.89</v>
+        <v>2489.71</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>31.59</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.32</v>
+        <v>1706.72</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>260.55</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>14.73</v>
+        <v>0</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>27.58</v>
+        <v>0</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>27.91</v>
+        <v>41.2</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>24.73</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -979,40 +979,40 @@
         <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>16.84</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>109.13</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>241.1</v>
+        <v>229.84</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>148.52</v>
+        <v>153.55</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>745.4</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>746.15</v>
+        <v>0</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>131.18</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>131.18</v>
+        <v>1278.12</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>0</v>
+        <v>869.47</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>125.97</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>204.22</v>
+        <v>211.14</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>64.79000000000001</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>169.46</v>
+        <v>46.83</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1091,25 +1091,25 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>163.96</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>163.96</v>
+        <v>875.42</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>44.5</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>595.53</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>72.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>19.41</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.57</v>
+        <v>10.54</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.8</v>
+        <v>39.29</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.18</v>
+        <v>10.15</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AA7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>108.94</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>284.56</v>
+        <v>54.11</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,25 +1285,25 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>136.33</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>136.33</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>318.28</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>427.03</v>
+        <v>680.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>129.95</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>73.62</v>
+        <v>462.6</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>110.4</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.62</v>
+        <v>0.02</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>129.51</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>
